--- a/outputs/cv/tabelas/cv_medio_10reg.xlsx
+++ b/outputs/cv/tabelas/cv_medio_10reg.xlsx
@@ -393,13 +393,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="D2">
-        <v>7.94</v>
+        <v>7.88</v>
       </c>
       <c r="E2">
-        <v>7.88</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="3">
@@ -417,10 +417,10 @@
         <v>1.97</v>
       </c>
       <c r="D3">
-        <v>8.380000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E3">
-        <v>8.15</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="4">
@@ -438,10 +438,10 @@
         <v>7.83</v>
       </c>
       <c r="D4">
-        <v>18.17</v>
+        <v>17.95</v>
       </c>
       <c r="E4">
-        <v>17.34</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="5">
@@ -456,13 +456,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
       <c r="D5">
-        <v>26.66</v>
+        <v>25.8</v>
       </c>
       <c r="E5">
-        <v>26.72</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="6">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="D6">
-        <v>11.87</v>
+        <v>11.76</v>
       </c>
       <c r="E6">
-        <v>11.09</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="7">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>5.43</v>
+        <v>5.47</v>
       </c>
       <c r="D7">
-        <v>13.13</v>
+        <v>13.02</v>
       </c>
       <c r="E7">
-        <v>12.43</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="8">
@@ -522,10 +522,10 @@
         <v>4.44</v>
       </c>
       <c r="D8">
-        <v>12.18</v>
+        <v>12.03</v>
       </c>
       <c r="E8">
-        <v>11.14</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="9">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="D9">
-        <v>10.63</v>
+        <v>10.52</v>
       </c>
       <c r="E9">
-        <v>9.68</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="10">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="D10">
-        <v>12.11</v>
+        <v>11.92</v>
       </c>
       <c r="E10">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="11">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C11">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="D11">
-        <v>11.98</v>
+        <v>11.84</v>
       </c>
       <c r="E11">
-        <v>11.3</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="12">
@@ -606,10 +606,10 @@
         <v>0.8</v>
       </c>
       <c r="D12">
-        <v>3.59</v>
+        <v>3.54</v>
       </c>
       <c r="E12">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="13">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="D13">
-        <v>8.970000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="14">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C14">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="D14">
-        <v>10.11</v>
+        <v>9.68</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>8.880000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D15">
-        <v>23.63</v>
+        <v>23.79</v>
       </c>
       <c r="E15">
-        <v>22.5</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="16">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>5.08</v>
+        <v>5.01</v>
       </c>
       <c r="D16">
-        <v>35.45</v>
+        <v>32.33</v>
       </c>
       <c r="E16">
-        <v>34.93</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="17">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="C17">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="D17">
-        <v>14.81</v>
+        <v>14.27</v>
       </c>
       <c r="E17">
-        <v>14.12</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="18">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="C18">
-        <v>4.97</v>
+        <v>5.17</v>
       </c>
       <c r="D18">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="E18">
-        <v>14.03</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="19">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C19">
-        <v>4.55</v>
+        <v>4.72</v>
       </c>
       <c r="D19">
-        <v>13.08</v>
+        <v>12.5</v>
       </c>
       <c r="E19">
-        <v>12.68</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="20">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="C20">
-        <v>5.29</v>
+        <v>5.26</v>
       </c>
       <c r="D20">
-        <v>13.05</v>
+        <v>12.75</v>
       </c>
       <c r="E20">
-        <v>11.82</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="21">
@@ -792,13 +792,13 @@
         </is>
       </c>
       <c r="C21">
-        <v>5.99</v>
+        <v>6.12</v>
       </c>
       <c r="D21">
-        <v>13.65</v>
+        <v>12.98</v>
       </c>
       <c r="E21">
-        <v>12.63</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="22">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="C22">
-        <v>5.2</v>
+        <v>5.39</v>
       </c>
       <c r="D22">
-        <v>14.59</v>
+        <v>14.1</v>
       </c>
       <c r="E22">
-        <v>14.26</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="23">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="D23">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="E23">
-        <v>4.26</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="24">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C24">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="D24">
-        <v>9.98</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E24">
-        <v>9.91</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="25">
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="C25">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="D25">
-        <v>10.88</v>
+        <v>10.73</v>
       </c>
       <c r="E25">
-        <v>10.79</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="26">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C26">
-        <v>8.949999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="D26">
-        <v>25.89</v>
+        <v>25.1</v>
       </c>
       <c r="E26">
-        <v>24.55</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="27">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C27">
-        <v>5.45</v>
+        <v>5.18</v>
       </c>
       <c r="D27">
-        <v>39.68</v>
+        <v>36.9</v>
       </c>
       <c r="E27">
-        <v>38.95</v>
+        <v>35.68</v>
       </c>
     </row>
     <row r="28">
@@ -942,10 +942,10 @@
         <v>4.93</v>
       </c>
       <c r="D28">
-        <v>15.42</v>
+        <v>15.6</v>
       </c>
       <c r="E28">
-        <v>14.86</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="29">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C29">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="D29">
-        <v>15.43</v>
+        <v>14.78</v>
       </c>
       <c r="E29">
-        <v>14.78</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="30">
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="C30">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="D30">
-        <v>13.59</v>
+        <v>12.49</v>
       </c>
       <c r="E30">
-        <v>13.36</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="31">
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="C31">
-        <v>5.48</v>
+        <v>5.62</v>
       </c>
       <c r="D31">
-        <v>14.18</v>
+        <v>13.87</v>
       </c>
       <c r="E31">
-        <v>13.12</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="32">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="C32">
-        <v>5.4</v>
+        <v>5.32</v>
       </c>
       <c r="D32">
-        <v>14.77</v>
+        <v>13.89</v>
       </c>
       <c r="E32">
-        <v>13.09</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="33">
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="C33">
-        <v>4.76</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>14.8</v>
+        <v>14.81</v>
       </c>
       <c r="E33">
-        <v>14.82</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="34">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D34">
-        <v>4.46</v>
+        <v>4.35</v>
       </c>
       <c r="E34">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
     </row>
   </sheetData>
